--- a/alimentacion_mapa_datajam_anual.xlsx
+++ b/alimentacion_mapa_datajam_anual.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Catalogos" sheetId="8" r:id="rId8"/>
     <sheet name="Fuentes y control" sheetId="9" r:id="rId9"/>
     <sheet name="Reportes Pepe" sheetId="10" r:id="rId10"/>
+    <sheet name="Reportes" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -454,7 +455,7 @@
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
   <threadedComment ref="N4" id="{54EE7951-7262-4200-6969-000000000000}" personId="{54EE7950-7262-4200-6969-000000000001}">
-    <text>Cobertura territorial distrital del aÃÂÃÂ±o. En 2025 baja a 82,3%.</text>
+    <text>Cobertura territorial distrital del aÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ±o. En 2025 baja a 82,3%.</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -698,6 +699,136 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Localidad</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Año</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Hora</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Arma</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Artículo</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Descripción</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Fuente</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Fecha Reporte</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Modalidad</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>robo_residencia</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Chapinero</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D2" t="str">
+        <v>23:45</v>
+      </c>
+      <c r="E2" t="str">
+        <v>arma_fuego</v>
+      </c>
+      <c r="F2" t="str">
+        <v>electrodomesticos</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Robo a residencia en zona residencial. Acceso por ventana posterior. Robaron TV y computadora</v>
+      </c>
+      <c r="H2" t="str">
+        <v>presencial</v>
+      </c>
+      <c r="I2" t="str">
+        <v>30/6/2026, 6:50:00 p. m.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>intento_hurto</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Barrios Unidos</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D3" t="str">
+        <v>12:13</v>
+      </c>
+      <c r="E3" t="str">
+        <v>arma_blanca</v>
+      </c>
+      <c r="F3" t="str">
+        <v>billetera_dinero</v>
+      </c>
+      <c r="G3" t="str">
+        <v>...</v>
+      </c>
+      <c r="H3" t="str">
+        <v>web</v>
+      </c>
+      <c r="I3" t="str">
+        <v>30/6/2026, 3:32:48 p. m.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>vehiculo</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Engativá</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D4" t="str">
+        <v>12:13</v>
+      </c>
+      <c r="E4" t="str">
+        <v>arma_blanca</v>
+      </c>
+      <c r="G4" t="str">
+        <v>...</v>
+      </c>
+      <c r="H4" t="str">
+        <v>whatsapp</v>
+      </c>
+      <c r="I4" t="str">
+        <v>30/6/2026, 7:36:52 p. m.</v>
+      </c>
+      <c r="J4" t="str">
+        <v>atraco</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
